--- a/supplementary_data_3_prompt_schema_config_freeze_inventory.xlsx
+++ b/supplementary_data_3_prompt_schema_config_freeze_inventory.xlsx
@@ -575,12 +575,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>AAS+</t>
+          <t>AD+</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>AAS-</t>
+          <t>AD-</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
